--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 4'!$A$1:$C$16</definedName>
@@ -472,7 +472,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.846929659457994</v>
+        <v>4.846929974563877</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.957808638228077</v>
+        <v>3.957808484702019</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.37045427921837</v>
+        <v>12.37045679568402</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.883502771604682</v>
+        <v>-8.883506473980374</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.5445684357997</v>
+        <v>38.54459229054199</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02739460758143</v>
+        <v>-32.02740473135195</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.846929659457994</v>
+        <v>4.846929974563877</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>4.010102220229272</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.535019476222</v>
+        <v>13.53502286281013</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.649552522801262</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.04632325911844539</v>
+        <v>-0.04632348391823537</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.518273050774795</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1272024714396536</v>
+        <v>0.1272020743932543</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8716040257792284</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3581028950843376</v>
+        <v>0.3581028287644549</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6804804586081132</v>
+        <v>0.6804802884945013</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.541348794502089</v>
+        <v>2.541348252319989</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 4'!$A$1:$C$16</definedName>
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.846929974563877</v>
+        <v>4.759474108721161</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.422856966733567</v>
+        <v>3.448521353622169</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.957808484702019</v>
+        <v>3.874489132034076</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.57522123893806</v>
+        <v>95.6140350877193</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.60176991150442</v>
+        <v>64.03508771929825</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.424778761061947</v>
+        <v>4.385964912280701</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.39823008849557</v>
+        <v>35.96491228070175</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.697222222222224</v>
+        <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.37045679568402</v>
+        <v>12.3704578842066</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.883506473980374</v>
+        <v>-8.791789686655342</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54459229054199</v>
+        <v>38.54459628071724</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740473135195</v>
+        <v>-32.02741816102964</v>
       </c>
     </row>
     <row r="10">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.846929974563877</v>
+        <v>4.759474108721161</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.010102220229272</v>
+        <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.53502286281013</v>
+        <v>13.50731721943351</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.649552522801262</v>
+        <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.04632348391823537</v>
+        <v>-0.03004063066969971</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.518273050774795</v>
+        <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1272020743932543</v>
+        <v>0.1259009991169342</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8716040257792284</v>
+        <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3581028287644549</v>
+        <v>0.3523626513985706</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.35776078315886</v>
+        <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6804802884945013</v>
+        <v>0.6696209906580181</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>92.0046082949309</v>
+        <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.541348252319989</v>
+        <v>2.505229331977628</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 4'!$A$1:$C$16</definedName>
@@ -472,7 +472,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.759474108721161</v>
+        <v>4.759474550358498</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3.448521353622169</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.874489132034076</v>
+        <v>3.87448954575127</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.3704578842066</v>
+        <v>12.3704579133961</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791789686655342</v>
+        <v>-8.791788510659671</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54459628071724</v>
+        <v>38.54465342164011</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741816102964</v>
+        <v>-32.02741339540493</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.759474108721161</v>
+        <v>4.759474550358498</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.50731721943351</v>
+        <v>13.50731790338343</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03004063066969971</v>
+        <v>-0.0300397442826129</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1259009991169342</v>
+        <v>0.1259025844626875</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3523626513985706</v>
+        <v>0.3523626662526618</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6696209906580181</v>
+        <v>0.6696211286574246</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.505229331977628</v>
+        <v>2.505229672990199</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -472,7 +472,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.759474550358498</v>
+        <v>4.759474260033616</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.3704579133961</v>
+        <v>12.37045721245495</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791788510659671</v>
+        <v>-8.791788069887311</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54465342164011</v>
+        <v>38.54460198478553</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741339540493</v>
+        <v>-32.02740638430635</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.759474550358498</v>
+        <v>4.759474260033616</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.50731790338343</v>
+        <v>13.50731527656471</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.0300397442826129</v>
+        <v>-0.03004051713995683</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1259025844626875</v>
+        <v>0.1259024146109362</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3523626662526618</v>
+        <v>0.3523627132840631</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6696211286574246</v>
+        <v>0.6696211014887262</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.505229672990199</v>
+        <v>2.505229656636168</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 4'!$A$1:$C$16</definedName>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.759474260033616</v>
+        <v>4.720955480839763</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448521353622169</v>
+        <v>3.448012329545969</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.87448954575127</v>
+        <v>3.843132845486785</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.6140350877193</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.03508771929825</v>
+        <v>64.34782608695652</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.385964912280701</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.96491228070175</v>
+        <v>35.65217391304348</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.721926605504589</v>
+        <v>3.718909090909091</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.37045721245495</v>
+        <v>12.20774455035246</v>
       </c>
     </row>
     <row r="7">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.8680000000000002</v>
+        <v>-0.868</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791788069887311</v>
+        <v>-8.791785766573398</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54460198478553</v>
+        <v>38.54462770320806</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740638430635</v>
+        <v>-32.02740161868049</v>
       </c>
     </row>
     <row r="10">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.759474260033616</v>
+        <v>4.720955480839763</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.001514378174758</v>
+        <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.50731527656471</v>
+        <v>13.45428483462503</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.626664430542024</v>
+        <v>2.638684739182457</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03004051713995683</v>
+        <v>-0.02170278602512823</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.443105350916397</v>
+        <v>8.543303212889626</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1259024146109362</v>
+        <v>0.1472125616225912</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8798204135639283</v>
+        <v>0.8834156315349503</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3523627132840631</v>
+        <v>0.3508886231314379</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.52592048115421</v>
+        <v>14.58478488287688</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6696211014887262</v>
+        <v>0.6671086844656693</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>93.47695852534564</v>
+        <v>94.25806451612902</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.505229656636168</v>
+        <v>2.50614502548762</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table 4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 4'!$A$1:$C$16</definedName>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.720955480839763</v>
+        <v>4.720955800193191</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3.448012329545969</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.843132845486785</v>
+        <v>3.843133091484296</v>
       </c>
     </row>
     <row r="4">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909091</v>
+        <v>3.718909090909092</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.20774455035246</v>
+        <v>12.20774600360396</v>
       </c>
     </row>
     <row r="7">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.868</v>
+        <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791785766573398</v>
+        <v>-8.791787493767707</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54462770320806</v>
+        <v>38.54462412563478</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740161868049</v>
+        <v>-32.02741339540493</v>
       </c>
     </row>
     <row r="10">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.720955480839763</v>
+        <v>4.720955800193191</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.45428483462503</v>
+        <v>13.45428494013697</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182457</v>
+        <v>2.638684739182456</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.02170278602512823</v>
+        <v>-0.0217036217385676</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.543303212889626</v>
+        <v>8.54330321288962</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1472125616225912</v>
+        <v>0.147212041724103</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349503</v>
+        <v>0.8834156315349508</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3508886231314379</v>
+        <v>0.350888644115867</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287688</v>
+        <v>14.58478488287689</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6671086844656693</v>
+        <v>0.6671086457840698</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612902</v>
+        <v>94.25806451612905</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.50614502548762</v>
+        <v>2.506144831481828</v>
       </c>
     </row>
   </sheetData>
